--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -8,15 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\quant_bet_alpha\football\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B0CF4D-266E-4EE2-AA6D-B8C1D47D8434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3376199E-3805-4F61-8FA4-763C73267DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stakes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -25,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Date </t>
   </si>
@@ -142,30 +151,6 @@
   </si>
   <si>
     <t>509.05</t>
-  </si>
-  <si>
-    <t>5/9/2026</t>
-  </si>
-  <si>
-    <t>8:35:47</t>
-  </si>
-  <si>
-    <t>12:59:31</t>
-  </si>
-  <si>
-    <t>5/10/2026</t>
-  </si>
-  <si>
-    <t>9:06:45</t>
-  </si>
-  <si>
-    <t>15:49:46</t>
-  </si>
-  <si>
-    <t>5/11/2026</t>
-  </si>
-  <si>
-    <t>18:10:13</t>
   </si>
   <si>
     <t>5/17/2026</t>
@@ -213,7 +198,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -227,8 +216,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3642E65D-2AA7-499A-8F2D-36E7575145E5}" name="Table1" displayName="Table1" ref="A1:V7" totalsRowShown="0">
-  <autoFilter ref="A1:V7" xr:uid="{3642E65D-2AA7-499A-8F2D-36E7575145E5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3642E65D-2AA7-499A-8F2D-36E7575145E5}" name="Table1" displayName="Table1" ref="A1:V10" totalsRowShown="0">
+  <autoFilter ref="A1:V10" xr:uid="{3642E65D-2AA7-499A-8F2D-36E7575145E5}"/>
   <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{87BEFA27-577C-4C9E-9E1F-F7CB17742C02}" name="Date "/>
     <tableColumn id="2" xr3:uid="{5F95BD95-B426-4963-A72E-CF81654FF2B8}" name="Time"/>
@@ -251,7 +240,9 @@
     <tableColumn id="19" xr3:uid="{E682FCAF-DFE5-4C56-B9AC-702BC3C88597}" name="Total Stake (GHS)"/>
     <tableColumn id="20" xr3:uid="{73F12DED-766E-4361-B192-15B74BC29A7B}" name=" Profit %"/>
     <tableColumn id="21" xr3:uid="{988133D7-2016-489B-B7EF-3E9262F7B1A4}" name=" Profit(GHS)"/>
-    <tableColumn id="22" xr3:uid="{BE5587F8-1BAB-4ED3-9848-AB4693771B42}" name="Accumulated Profit (GHS)"/>
+    <tableColumn id="22" xr3:uid="{BE5587F8-1BAB-4ED3-9848-AB4693771B42}" name="Accumulated Profit (GHS)" dataDxfId="0">
+      <calculatedColumnFormula>SUM(U$2:U2)</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -542,10 +533,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="1" max="1" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+    <col min="4" max="4" width="36.21875" customWidth="1"/>
     <col min="6" max="6" width="9" customWidth="1"/>
     <col min="7" max="7" width="11.6640625" customWidth="1"/>
     <col min="10" max="10" width="14.21875" customWidth="1"/>
@@ -679,56 +673,35 @@
       <c r="U2" t="s">
         <v>38</v>
       </c>
-      <c r="V2" t="s">
-        <v>38</v>
+      <c r="V2">
+        <f>SUM(U$2:U2)</f>
+        <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" t="s">
-        <v>46</v>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V8">
+        <f>SUM(U$2:U8)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" t="s">
-        <v>48</v>
+      <c r="V9">
+        <f>SUM(U$2:U10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V10">
+        <f>SUM(U$2:U10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\quant_bet_alpha\football\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3376199E-3805-4F61-8FA4-763C73267DCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C2E7B51-621D-4486-9224-E265DEEE85B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -539,11 +539,15 @@
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
     <col min="2" max="2" width="14.88671875" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="36.21875" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.21875" customWidth="1"/>
+    <col min="4" max="4" width="37.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="15.21875" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" customWidth="1"/>
+    <col min="10" max="10" width="17" customWidth="1"/>
     <col min="11" max="11" width="11.6640625" customWidth="1"/>
+    <col min="13" max="13" width="12.21875" customWidth="1"/>
     <col min="14" max="14" width="14.21875" customWidth="1"/>
     <col min="15" max="15" width="11.6640625" customWidth="1"/>
     <col min="18" max="18" width="14.21875" customWidth="1"/>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,10 +599,6 @@
           <t>127.27</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>1400</t>
@@ -635,26 +631,6 @@
           <t>8:35:47</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -667,26 +643,6 @@
           <t>12:59:31</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -699,26 +655,6 @@
           <t>9:06:45</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -731,26 +667,6 @@
           <t>15:49:46</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -763,50 +679,6 @@
           <t>18:10:13</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -819,26 +691,157 @@
           <t>10:45:36</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>09:51:48</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Appalachian FC vs Hickory FC</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>USA. USL League Two</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6/6/2026 23:00</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>305.16</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Sportybet</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1094.84</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U10" t="n">
+        <v>34.24</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>09:51:49</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Appalachian FC vs Hickory FC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>USA. USL League Two</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>6/6/2026 23:00</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>303.33</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Football.com</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1096.67</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U11" t="n">
+        <v>25.67</v>
+      </c>
+      <c r="V11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,10 +828,6 @@
       <c r="N11" t="n">
         <v>1096.67</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>1400</v>
       </c>
@@ -841,7 +837,84 @@
       <c r="U11" t="n">
         <v>25.67</v>
       </c>
-      <c r="V11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>09:53:01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque vs Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Uruguay. Primera Division</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6/6/2026 18:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>22Bet</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MSport</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1294.52</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U12" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="V12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -1,165 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\quant_bet_alpha\football\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25607A8D-A57D-4432-A573-A31EEAC78F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stakes" sheetId="1" r:id="rId1"/>
+    <sheet name="Stakes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
-  <si>
-    <t xml:space="preserve">Date </t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Match</t>
-  </si>
-  <si>
-    <t>Tournament</t>
-  </si>
-  <si>
-    <t>Kickoff</t>
-  </si>
-  <si>
-    <t>Market</t>
-  </si>
-  <si>
-    <t>Platform 1</t>
-  </si>
-  <si>
-    <t>Bet 1</t>
-  </si>
-  <si>
-    <t>Odds 1</t>
-  </si>
-  <si>
-    <t>Stake 1 (GHS)</t>
-  </si>
-  <si>
-    <t>Platform 2</t>
-  </si>
-  <si>
-    <t>Bet 2</t>
-  </si>
-  <si>
-    <t>Odds 2</t>
-  </si>
-  <si>
-    <t>Stake 2 (GHS)</t>
-  </si>
-  <si>
-    <t>Platform 3</t>
-  </si>
-  <si>
-    <t>Bet 3</t>
-  </si>
-  <si>
-    <t>Odds 3</t>
-  </si>
-  <si>
-    <t>Stake 3 (GHS)</t>
-  </si>
-  <si>
-    <t>Total Stake (GHS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Profit %</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Profit(GHS)</t>
-  </si>
-  <si>
-    <t>Accumulated Profit (GHS)</t>
-  </si>
-  <si>
-    <t>6/6/2026</t>
-  </si>
-  <si>
-    <t>9:16:49</t>
-  </si>
-  <si>
-    <t>Central Espanol FC vs Racing Club Montevideo</t>
-  </si>
-  <si>
-    <t>Uruguay. Primera Division</t>
-  </si>
-  <si>
-    <t>6/6/2026 13:00</t>
-  </si>
-  <si>
-    <t>Over/Under 0.5</t>
-  </si>
-  <si>
-    <t>MSport</t>
-  </si>
-  <si>
-    <t>Over 0.5</t>
-  </si>
-  <si>
-    <t>1.1</t>
-  </si>
-  <si>
-    <t>1272.73</t>
-  </si>
-  <si>
-    <t>22Bet</t>
-  </si>
-  <si>
-    <t>Under 0.5</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>127.27</t>
-  </si>
-  <si>
-    <t>1400</t>
-  </si>
-  <si>
-    <t>2.48</t>
-  </si>
-  <si>
-    <t>509.05</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -178,22 +46,119 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V13" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:V10"/>
+  <tableColumns count="22">
+    <tableColumn id="1" name="Date "/>
+    <tableColumn id="2" name="Time"/>
+    <tableColumn id="3" name="Match"/>
+    <tableColumn id="4" name="Tournament"/>
+    <tableColumn id="5" name="Kickoff"/>
+    <tableColumn id="6" name="Market"/>
+    <tableColumn id="7" name="Platform 1"/>
+    <tableColumn id="8" name="Bet 1"/>
+    <tableColumn id="9" name="Odds 1"/>
+    <tableColumn id="10" name="Stake 1 (GHS)"/>
+    <tableColumn id="11" name="Platform 2"/>
+    <tableColumn id="12" name="Bet 2"/>
+    <tableColumn id="13" name="Odds 2"/>
+    <tableColumn id="14" name="Stake 2 (GHS)"/>
+    <tableColumn id="15" name="Platform 3"/>
+    <tableColumn id="16" name="Bet 3"/>
+    <tableColumn id="17" name="Odds 3"/>
+    <tableColumn id="18" name="Stake 3 (GHS)"/>
+    <tableColumn id="19" name="Total Stake (GHS)"/>
+    <tableColumn id="20" name=" Profit %"/>
+    <tableColumn id="21" name=" Profit(GHS)"/>
+    <tableColumn id="22" name="Accumulated Profit (GHS)" dataDxfId="0">
+      <calculatedColumnFormula>SUM(U$2:U2)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -480,135 +445,496 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <cols>
+    <col width="19.44140625" customWidth="1" min="1" max="1"/>
+    <col width="14.88671875" customWidth="1" min="2" max="2"/>
+    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="37.33203125" customWidth="1" min="4" max="4"/>
+    <col width="19.109375" customWidth="1" min="5" max="5"/>
+    <col width="21.44140625" customWidth="1" min="6" max="6"/>
+    <col width="13.6640625" customWidth="1" min="7" max="7"/>
+    <col width="15.21875" customWidth="1" min="8" max="8"/>
+    <col width="11.5546875" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="11.6640625" customWidth="1" min="11" max="11"/>
+    <col width="12.21875" customWidth="1" min="13" max="13"/>
+    <col width="14.21875" customWidth="1" min="14" max="14"/>
+    <col width="11.6640625" customWidth="1" min="15" max="15"/>
+    <col width="14.21875" customWidth="1" min="18" max="18"/>
+    <col width="17.44140625" customWidth="1" min="19" max="19"/>
+    <col width="9.88671875" customWidth="1" min="20" max="20"/>
+    <col width="12.77734375" customWidth="1" min="21" max="21"/>
+    <col width="24.33203125" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Date </t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Match</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Tournament</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Kickoff</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Platform 1</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Bet 1</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Odds 1</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Stake 1 (GHS)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Platform 2</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Bet 2</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Odds 2</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Stake 2 (GHS)</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Platform 3</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Bet 3</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>Odds 3</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Stake 3 (GHS)</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Total Stake (GHS)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Profit %</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Profit(GHS)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Accumulated Profit (GHS)</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H2" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>33</v>
-      </c>
-      <c r="M2" t="s">
-        <v>34</v>
-      </c>
-      <c r="N2" t="s">
-        <v>35</v>
-      </c>
-      <c r="S2" t="s">
-        <v>36</v>
-      </c>
-      <c r="T2" t="s">
-        <v>37</v>
-      </c>
-      <c r="U2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V2" t="s">
-        <v>38</v>
-      </c>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>9:16:49</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Central Espanol FC vs Racing Club Montevideo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Uruguay. Primera Division</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>6/6/2026 13:00</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Over/Under 0.5</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>MSport</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>1272.73</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>22Bet</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Under 0.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>127.27</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>509.05</t>
+        </is>
+      </c>
+      <c r="V2">
+        <f>SUM(U$2:U2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="V8">
+        <f>SUM(U$2:U8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="V9">
+        <f>SUM(U$2:U10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="V10">
+        <f>SUM(U$2:U10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>5/17/2026</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>10:45:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>09:56:37</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Appalachian FC vs Hickory FC</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>USA. USL League Two</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6/6/2026 23:00</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>305.16</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Sportybet</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1094.84</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U12" t="n">
+        <v>34.24</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>09:56:37</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Appalachian FC vs Hickory FC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>USA. USL League Two</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6/6/2026 23:00</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>303.33</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Football.com</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N13" t="n">
+        <v>1096.67</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U13" t="n">
+        <v>25.67</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>09:56:37</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Montevideo City Torque vs Deportivo Maldonado</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Uruguay. Primera Division</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>6/6/2026 18:00</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>22Bet</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>MSport</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1294.52</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U14" t="n">
+        <v>23.97</v>
+      </c>
+      <c r="V14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V13" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V14" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:V10"/>
   <tableColumns count="22">
     <tableColumn id="1" name="Date "/>
@@ -916,10 +916,6 @@
       <c r="N14" t="n">
         <v>1294.52</v>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
         <v>1400</v>
       </c>
@@ -929,7 +925,6 @@
       <c r="U14" t="n">
         <v>23.97</v>
       </c>
-      <c r="V14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V14" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V15" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:V10"/>
   <tableColumns count="22">
     <tableColumn id="1" name="Date "/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.44140625" customWidth="1" min="1" max="1"/>
@@ -926,6 +926,84 @@
         <v>23.97</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:03:08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Appalachian FC vs Hickory FC</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>USA. USL League Two</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>6/6/2026 23:00</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Over/Under 4.5</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Over 4.5</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>323.08</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Football.com</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Under 4.5</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1076.92</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U15" t="n">
+        <v>118.48</v>
+      </c>
+      <c r="V15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -129,8 +129,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V15" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:V10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V16" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:V15"/>
   <tableColumns count="22">
     <tableColumn id="1" name="Date "/>
     <tableColumn id="2" name="Time"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.44140625" customWidth="1" min="1" max="1"/>
@@ -677,36 +677,6 @@
         <v/>
       </c>
     </row>
-    <row r="8">
-      <c r="V8">
-        <f>SUM(U$2:U8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="V9">
-        <f>SUM(U$2:U10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="V10">
-        <f>SUM(U$2:U10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>5/17/2026</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>10:45:36</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -989,10 +959,6 @@
       <c r="N15" t="n">
         <v>1076.92</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
         <v>1400</v>
       </c>
@@ -1002,7 +968,84 @@
       <c r="U15" t="n">
         <v>118.48</v>
       </c>
-      <c r="V15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>6/6/2026</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10:04:25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Central Espanol FC vs Racing Club Montevideo</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Uruguay. Primera Division</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6/6/2026 13:00</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Over/Under 0.5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1296.3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>22Bet</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Under 0.5</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" t="n">
+        <v>103.7</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>1400</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="V16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/football/data/stake_tracker.xlsx
+++ b/football/data/stake_tracker.xlsx
@@ -129,7 +129,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V16" headerRowCount="1" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:V17" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:V16"/>
   <tableColumns count="22">
     <tableColumn id="1" name="Date "/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.44140625" customWidth="1" min="1" max="1"/>
@@ -677,15 +677,6 @@
         <v/>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -1050,6 +1041,84 @@
       <c r="U16" t="n">
         <v>155.5</v>
       </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>6/24/2026</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>08:49:15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Dragonas IDV vs CS Emelec</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ecuador. Superliga, Women</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6/24/2026 16:00</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Double Chance 12 vs X</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Sportybet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>12 (Home/Away)</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J17" t="n">
+        <v>986.6799999999999</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Betway</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Draw</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>80</v>
+      </c>
+      <c r="N17" t="n">
+        <v>13.32</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="T17" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>65.61</v>
+      </c>
+      <c r="V17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
